--- a/docs/downloads/09/t8_transition_alaotra_avaradrano.xlsx
+++ b/docs/downloads/09/t8_transition_alaotra_avaradrano.xlsx
@@ -443,12 +443,6 @@
           <t>Manioc</t>
         </is>
       </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -466,12 +460,6 @@
           <t>Maïs</t>
         </is>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -489,12 +477,6 @@
           <t>Patate douce</t>
         </is>
       </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -512,12 +494,6 @@
           <t>Manioc</t>
         </is>
       </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -535,12 +511,6 @@
           <t>Patate douce</t>
         </is>
       </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -558,12 +528,6 @@
           <t>Autres mélanges</t>
         </is>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,12 +545,6 @@
           <t>Maïs</t>
         </is>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -604,12 +562,6 @@
           <t>Maïs</t>
         </is>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -627,12 +579,6 @@
           <t>Riz</t>
         </is>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -649,12 +595,6 @@
         <is>
           <t>Tubercule+Céréale</t>
         </is>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1.1</v>
       </c>
     </row>
     <row r="14">
